--- a/App-audit-and-tasks.xlsx
+++ b/App-audit-and-tasks.xlsx
@@ -1764,260 +1764,1180 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="7" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>A-017</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Ask AI answers render as one plain paragraph. AskAiView prints a.summary inside a &lt;p&gt;, and the narration system prompt returns a flat string, so lists, headings, bold and tables the model could produce are flattened or shown as raw asterisks.</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Phase 4 - UX &amp; Accessibility</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>AI Bridge</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Render Ask AI answers as formatted Markdown (headings, lists, bold, tables, code) instead of a plain paragraph</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>src/components/AskAiView.jsx:379 (&lt;p className="askai-answer-text"&gt;{a.summary}&lt;/p&gt;); src/services/askAi.js:1077-1107 narrate() + NARRATE_SYSTEM; src/components/Markdown.jsx:134 (existing renderer + .markdown-preview styles)
+Verified: renderMarkdown in the browser — pipe tables (with :--:/--: alignment), ``` fences, headings, lists, bold all render; raw &lt;img&gt;/&lt;script&gt;/&lt;b&gt; from the model are escaped (no dangerouslySetInnerHTML of unsanitised text); no literal ** or | survive. Table styled with --c-border/--c-surface-2 and scrolls in .markdown-table-wrap; screenshot confirms dark mode. Fold switched from -webkit-line-clamp to max-height+mask so block content clamps cleanly. answerToText now emits Markdown. NARRATE_SYSTEM asks for GFM; maxTokens 900 -&gt; 1400.</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>1) In narrate(): change NARRATE_SYSTEM so `summary` is GitHub-flavoured Markdown (allow ##/### headings, bullet and numbered lists, **bold**, inline code, simple pipe tables; no HTML, no code fences around the whole answer) and keep the JSON envelope {summary, actions, followUps}. 2) In AskAiView replace the &lt;p&gt; with &lt;div className="askai-answer-text markdown"&gt;&lt;Markdown src={a.summary} /&gt;&lt;/div&gt; for AI answers; keep local (aiUsed=false) summaries as plain text or wrap them in the same component (they are safe strings). 3) Confirm renderMarkdown escapes HTML (no dangerouslySetInnerHTML of raw model output without sanitising) and supports tables; if tables are missing, add a minimal pipe-table renderer in Markdown.jsx. 4) Keep the fold/'Show more' behaviour working on the new block (max-height + fade already keyed off .askai-answer-text). 5) answerToText() (copy button) should copy the raw Markdown so it pastes cleanly into docs/chat. 6) Add CSS for .askai-answer-text table/th/td using --c-border and --c-surface-2 so tables read in dark mode.</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Ask a question like 'summarise this week by project' and the answer shows real headings, bullets, bold and a table where appropriate; copy still yields readable Markdown.</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>In Ask AI (bridge on) ask 'List my overdue tasks grouped by project with a table of hours'. Answer renders bullets/headings/table (no literal ** or |). Toggle Show more/less still works. Copy answer → paste in a text editor shows Markdown. Dark mode: table borders visible. No console errors.</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>S (~1h)</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n"/>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="7" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>A-018</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>The due-task alert stacks task details above the GenAI prompt block in one 640px column, so on desktop the prompt/answer pushes the action buttons below the fold and the user scrolls to reach Done / Snooze.</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Phase 4 - UX &amp; Accessibility</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>TaskEditor</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Split the due-task alert into two columns: left = task details, right = 'Prompt to fulfil this task'</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>src/components/DueTaskAlertModal.jsx AlertDialog() (header, meta, description, &lt;PromptBlock&gt;, actions); src/App.css .due-alert* rules and the existing .modal-2col / .modal-2col-grid pattern (App.css:1006-1024)
+Verified in dev/due-alert.html at 1280px and 375px. Desktop: .due-alert-grid 369px/517px, max-width 960px, border-left divider (dark #3d4f66, screenshot). A 4000px answer injected into the right column -&gt; asideScrolls true, overflow auto, actions still on screen (bottom 536 of 900). 375px: single column, actionsBeforePrompt true, no horizontal scroll. Tab order = DOM order: x, Done, Snooze, caret, Skip, Open task, then the prompt column; focus starts on Snooze; Esc/D/S unchanged. Also fixed a pre-existing mobile bug where `.due-alert-actions .btn` stretched the snooze caret to 100%. Harness gained ?nb=1.</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>1) In AlertDialog wrap the body in &lt;div className="due-alert-grid"&gt;: left column = title, due badge, project/priority/due/requestedBy meta, description (Markdown), open-subtask list (render task.subtasks with done state, read-only), and the action row (Done / Snooze / Skip today / Open task) pinned at the bottom of the left column; right column = &lt;PromptBlock&gt; (prompt, Edit/Copy/Regenerate/Run, Run result) filling the column with its own scroll (max-height ~70vh). 2) Keep the header row (due badge, 'N more due after this', × close-all) full-width above the grid. 3) Add .due-alert.modal-2col sizing: max-width 960px, grid-template-columns minmax(300px, 5fr) minmax(360px, 7fr), gap 24px, a 1px divider (border-left var(--c-border)) on the right column. 4) Under 720px collapse to one column in the order: header → task details → actions → prompt (prompt last so buttons stay reachable on phones); keep the bottom-sheet behaviour from A-014. 5) Focus order: Snooze first, Tab through actions, then into the prompt column; keep the focus trap and D/S/Esc shortcuts. 6) Update dev/due-alert.html harness (no change needed to props) and re-check at 1280px and 375px.</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>On desktop the alert shows the task on the left with its buttons always visible, and the prompt/answer workspace on the right; on phones it stacks with the buttons before the prompt.</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Open harness at 1280px: two columns, action buttons visible without scrolling even after Run produces a long answer (answer scrolls inside the right column). At 375px: single column, buttons above the prompt, no horizontal scroll. Tab from Snooze reaches every control; Esc still snoozes. Dark mode divider visible.</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>A-005, A-007, A-014</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>S (~1h)</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="7" t="n"/>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>A-019</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>The app's AI answers come from the model's general memory. Ace wants a knowledge-base layer backed by his own Google NotebookLM notebooks via the unofficial `notebooklm` CLI (guide: ~/Developer/SKILLS/NOTEBOOKLM-CLI-INSTRUCTION.md). First step of the guide is to confirm the CLI surface on this machine and record operator prerequisites.</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Phase 5 - Polish &amp; Docs</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the notebooklm CLI command surface and document operator prerequisites (dedicated Google account, NOTEBOOKLM_HOME)</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>~/.local/bin/notebooklm (pipx, installed on this Mac; `notebooklm --help` verified 2026-09-07: auth check / list / source list|add / ask -n -c --json --quiet); README.md:45 ('AI brain — the Claude Code CLI' section to extend)
+Verified on this machine 2026-09-07: notebooklm 0.7.3 at ~/.local/bin/notebooklm. Exact argv recorded in the header comment of bridge/notebooklm.mjs (auth check --test --json; list --json; source list -n --json; source add &lt;content&gt; -n --type url|text --title --json; ask [Q] -n [-c] --json | --prompt-file -). `source add --type text --title` exists, so addSourceText needs NO temp file. --new documented as DESTRUCTIVE and never passed. README gained 'Knowledge base - NotebookLM (optional)' with pipx/login/dedicated-account/NOTEBOOKLM_HOME.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Run `notebooklm --version`, `notebooklm auth check --test --json`, `notebooklm list --json`, `notebooklm source add --help`, `notebooklm ask --help` and paste the exact flags into a short comment block at the top of bridge/notebooklm.mjs (A-020) so argv arrays are traceable. Note: `ask` has `--prompt-file -` (stdin) which avoids shell-length limits for long questions; `--new` is DESTRUCTIVE (deletes the server-side conversation) — never pass it. Add a README section 'Knowledge base — NotebookLM (optional)': `brew install pipx &amp;&amp; pipx ensurepath`, `pipx install "notebooklm-py[browser]"`, `notebooklm login` with a DEDICATED Google account, optional `NOTEBOOKLM_HOME=~/.notebooklm-sandbox`, and the statement that the whole feature is optional — app installs, starts and passes tests with the CLI absent. Notebooks are created/populated at notebooklm.google.com.</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>A reader knows how to install and sign in the CLI, which account to use, and the exact argv the bridge will call.</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>README renders the new section; the argv comment in bridge/notebooklm.mjs matches `--help` output on this machine.</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>XS (&lt;15m)</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="7" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>A-020</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Nothing in the repo can talk to NotebookLM. The guide's non-negotiables (PATH resolution, missing CLI = state not exception, boolean `error` flag, lenient JSON, 2-call semaphore, per-op timeouts) must live in ONE module, and in this repo the only process allowed to spawn CLIs is the local bridge.</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1 - Correctness</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>AI Bridge</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Create bridge/notebooklm.mjs: the single module that shells out to `notebooklm` (findCli, runCli, semaphore, lenient JSON, SETUP_HINT)</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>bridge/ai.mjs:80-91 (claudeCliAvailable / cliVersion pattern), bridge/ai.mjs:47-62 (CONFIG_FILE persistence pattern); guide §2.1–2.6, §3
+Verified by bridge/notebooklm.test.mjs (A-024): TM_NOTEBOOKLM_BIN=none -&gt; runCli resolves {ok:false, error contains 'pipx install'}; a fixture printing {"error":true,...,"message":"No notebook found"} + exit 1 -&gt; error is the message, never 'true'; 4 concurrent runCli calls -&gt; measured peak concurrency 2. Live: the real signed-out CLI exits with error:true and the bridge surfaced its real message. Timeouts 120/60/90/300/300s, maxBuffer 16MB, --quiet prepended, execFile + stdin for --prompt-file.</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>New ESM module, no imports from the frontend. Exports: SETUP_HINT (one string: `pipx install "notebooklm-py[browser]"` then `notebooklm login` with a dedicated Google account; picked up on Re-check, no restart), findCli() (order: env TM_NOTEBOOKLM_BIN — literal 'none' forces not-found; `which notebooklm` first line; ~/.local/bin, /opt/homebrew/bin, /usr/local/bin; null; cached), setCliResolver(fn) test hook, cliEnv() (honour NOTEBOOKLM_HOME, default to ~/.notebooklm-sandbox if that dir exists), parseJsonLenient(text) (whole → first { or [ → null), runCli(args,{timeoutMs}) → {ok,data}|{ok:false,error} never throws; execFile with maxBuffer 16 MB and `--quiet` prepended; error message order: payload.error ONLY if string → payload.message → stderr tail 1500 chars → timeout text when err.killed → err.message; FIFO semaphore MAX_CONCURRENT=2. Timeouts as constants: default 120 s, auth 60 s, list 90 s, ask 300 s, source add 300 s. Never spawn from anywhere else (add to CLAUDE.md pitfalls in A-032).</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Any part of the bridge can call runCli and get a normalised result; with the CLI missing the result is a readable setup hint, not a crash.</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Unit tests in A-024 pass: TM_NOTEBOOKLM_BIN=none → runCli resolves {ok:false,error contains 'pipx install'}; fixture script printing {"error":true,"message":"No notebook found"} + exit 1 → error === message, never 'true'; 3 parallel runCli calls: at most 2 in flight.</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>A-019</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>M (~half day)</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="7" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>A-021</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Every CLI call is a subprocess plus a Google round-trip; the UI will need status and notebook lists constantly. Without caching and a manual re-check, pickers block and a user who logs in while the app runs stays stuck.</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1 - Correctness</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>AI Bridge</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Add knowledgeStatus / listNotebooks / cachedNotebooks / resetKnowledgeCaches with TTL caches and response normalisation</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>bridge/notebooklm.mjs (A-020); bridge/ai.mjs:93-105 (detectProvider TTL cache pattern); guide §2.7, §2.8, §2.11
+Verified by unit tests: knowledgeStatus twice inside the TTL = one spawn (counted through setCliResolver), resetKnowledgeCaches makes the next call probe again; normalizeNotebooks handles array / {notebooks} / {items} and id|notebook_id|uuid, dropping id-less rows; signed-out fixture -&gt; authenticated false + login hint. cachedNotebooks() is a sync peek returning null when never fetched. Three distinct hints (SETUP_HINT / LOGIN_HINT / EMPTY_HINT) selected by knowledgeHint(). Field names checked against real `auth check --test --json`.</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>knowledgeStatus({force}) → { cliFound, cliPath, authenticated, hint, error } cached 60 s; authenticated = res.ok &amp;&amp; data.status==='ok' &amp;&amp; data.checks?.token_fetch (verify field names against `auth check --test --json` output on this machine). listNotebooks({force}) → [{ id, title, sourceCount }] cached 5 min, normalising data | data.notebooks | data.items and id | notebook_id | uuid, dropping entries without id. cachedNotebooks() synchronous peek (null if never fetched) — used by validators/pickers so they NEVER trigger a CLI call. resetKnowledgeCaches() clears path/status/notebooks. Distinct hints for: CLI missing (SETUP_HINT), present-not-signed-in ('Run `notebooklm login`… then Re-check'), signed-in-zero-notebooks ('Create one at notebooklm.google.com…').</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Status and notebook list are cheap to read repeatedly; a manual Re-check picks up a fresh `notebooklm login` without restarting the bridge.</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Call knowledgeStatus twice within 60 s → one CLI spawn (assert via setCliResolver counter). listNotebooks normalises the three payload shapes in a unit test. After resetKnowledgeCaches the next call spawns again.</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>A-020</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>S (~1h)</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n"/>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>A-022</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>The bridge needs the actual operations — list/add sources and ask — plus a local ask log, because NotebookLM exposes no history and the usage view has nothing to read otherwise.</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1 - Correctness</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>AI Bridge</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Implement listSources, addSourceUrl, addSourceText, askNotebook with answer normalisation and a persisted ask log</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>bridge/notebooklm.mjs; bridge/ai.mjs:110-131 (in-memory _usage + getUsage pattern) and :47-62 (CONFIG_FILE on disk); guide §2.9, §2.10, §2.11
+Implemented with normalisation + a persisted ask log at ~/.task-monitor/knowledge-asks.json (cap 500, trim on insert). Unit-verified: normalizeAnswer across answer|response|text|raw, object answers stringified, conversation_id|conversationId, citations|sources|references; log trimming at exactly 500 keeps the newest; question truncated to 300; notebookAskStats / recentAsks / rateAsk. addSourceText uses `--type text --title` so there is NO temp dir to leak. askNotebook uses --prompt-file - past 2000 chars (verified via an argv/stdin echo fixture) and never sends --new.
+PENDING OPERATOR STEP: the remaining live check needs `notebooklm login` with a dedicated Google account — a sign-in only Ace can perform.</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>listSources(id) → [{ id, title, kind }] (type|kind). addSourceUrl(id,url): validate /^https?:\/\//, argv ['source','add',url,'-n',id,'--json'], 300 s. addSourceText(id,title,text): check `source add --help` for a text flag first; otherwise mkdtemp → sanitised `&lt;title&gt;.txt` → source add &lt;path&gt; → rm -rf in finally. askNotebook(id, question, { conversationId, source:'manual'|'ask-ai'|'grounding'|'task-prompt', ...callerIds }) → { answer, citations, conversationId, ms, askId }; use `--prompt-file -` with stdin for questions &gt; 2000 chars; never pass --new. normalizeAnswer: answer|response|text|raw (stringify objects), conversation_id|conversationId, citations|sources. Ask log persisted next to the bridge CONFIG_FILE as knowledge-asks.json: { id, at, notebookId, question(≤300), ms, source, citationsCount, workspaceId?, projectId?, taskId?, helpful:null }, cap 500, trim on insert. Export notebookAskStats(id) → { total, last7d, lastAt }, recentAsks(id,n), rateAsk(askId, helpful|null).</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>The bridge can read sources, add URL/text sources, and ask a notebook, and every ask is recorded locally with who/what/when.</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>With the real CLI (manual, not in tests): `node -e` script asks a test notebook and prints answer + citations; knowledge-asks.json gains one row; addSourceText leaves no temp dir behind (ls $TMPDIR). Unit tests cover normalizeAnswer shapes and log trimming at 500.</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>A-020, A-021</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>M (~half day)</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="n"/>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>A-023</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>The frontend can only reach the CLI through the bridge's HTTP surface (127.0.0.1:4319, origin allowlist). No /knowledge routes exist.</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Phase 2 - Data &amp; Security</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>AI Bridge</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Expose /knowledge/* routes on the bridge (status, refresh, notebooks, sources, ask, usage, rate) returning 502 for CLI failures</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>bridge/server.mjs:108-150 (route switch, send(), readBody, cors); guide §4 endpoints
+Verified with curl against a live bridge. CLI present: GET /knowledge/status -&gt; cliFound true, cliPath ~/.local/bin/notebooklm, authenticated false, hint, error null. GET /knowledge/notebooks -&gt; 502 carrying the CLI's own message. TM_NOTEBOOKLM_BIN=none: status cliFound false with the pipx hint, notebooks -&gt; 502, /health still 200 with knowledge:{cliFound:false,authenticated:false} read from cache (never spawns). 400s verified for a bad kind and for ftp://; PATCH /knowledge/asks/&lt;unknown&gt; -&gt; 404. PATCH added to the CORS methods; origin allowlist unchanged. npm test unaffected (49 pass).</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Add cases: GET /knowledge/status; POST /knowledge/status/refresh (resetKnowledgeCaches + knowledgeStatus({force:true}) + listNotebooks({force:true})); GET /knowledge/notebooks; GET /knowledge/sources?notebook=&lt;id&gt;; POST /knowledge/sources { notebook, kind:'url'|'text', url|title+text } → 400 on bad kind/url; POST /knowledge/ask { notebook, question, conversationId?, source?, workspaceId?, projectId?, taskId? }; GET /knowledge/usage?notebook=&lt;id&gt; → { stats, recent }; PATCH /knowledge/asks/&lt;id&gt; { helpful }. Map { ok:false } → HTTP 502 with { error } (upstream dependency, message already user-readable). Add `knowledge: { cliFound, authenticated }` to healthPayload() (from the cached status only — never spawn in /health). Keep the existing origin allowlist; no new origins.</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>curl against the bridge returns status, notebooks and answers; a CLI failure is a 502 with the CLI's real message.</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>`curl -s 127.0.0.1:4319/knowledge/status` → JSON with cliFound true on this machine; `TM_NOTEBOOKLM_BIN=none npm run bridge` → status cliFound false, /knowledge/notebooks → 502 with pipx hint, /health still 200. npm test unaffected.</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>A-021, A-022</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>S (~1h)</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n"/>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="6" t="n"/>
-      <c r="J24" s="6" t="n"/>
-      <c r="K24" s="7" t="n"/>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>A-024</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>The guide's failure modes (missing CLI, boolean `error`, progress lines before JSON, timeouts, concurrency) are exactly the ones that shipped broken elsewhere; without tests they will regress here too. Tests must never spawn the real CLI.</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1 - Correctness</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Write bridge/notebooklm.test.mjs covering the guide's §5 list with fixture scripts instead of the real CLI</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>bridge/ai.test.mjs (style: node:test, pure functions); package.json test script already globs bridge/*.test.mjs
+Verified: 24 new cases, npm test 49 pass / 0 fail, and the real CLI is never spawned (every case drives a temp fixture script through setCliResolver). Covers missing CLI, the boolean `error` regression, exit-0-with-error, errorMessage ordering, parseJsonLenient (clean / after progress lines / garbage / empty), a 500ms timeout on a 3s fixture, peak concurrency &lt;= 2, normalizeNotebooks / normalizeAnswer / normalizeSources shapes, argv (no --new) + stdin, client-side URL and empty-text rejection, and the ask log. Counter-check: rewriting runCli to use payload.error first fails cases 4-6, then passes again when restored.</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Cases: (1) TM_NOTEBOOKLM_BIN=none → knowledgeStatus cliFound:false, hint contains 'pipx install'; SETUP_HINT contains 'notebooklm login'. (2) askNotebook with no CLI rejects with the setup hint, does not hang (await with a 2 s race). (3) Regression: setCliResolver → fixture .mjs script (written to a temp dir in the test, chmod +x, `#!/usr/bin/env node`) printing {"error":true,"code":"VALIDATION_ERROR","message":"No notebook found"} and exit 1 → thrown message contains 'No notebook found' and !== 'true'. (4) parseJsonLenient: clean JSON, JSON after progress lines, garbage → null. (5) Fixture that sleeps 3 s: runCli with timeoutMs 500 → error mentions 'timed out'. (6) Semaphore: fixture sleeping 300 ms, 4 concurrent runCli → measured peak concurrency ≤ 2. (7) normalizeNotebooks / normalizeAnswer shape variants. (8) Ask-log cap 500 and rateAsk. Restore env + resolver in afterEach.</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>npm test proves the integration degrades correctly and that the literal string 'true' can never reach a user.</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>npm test → all new cases pass; temporarily break the error-order in runCli (use payload.error first) and watch case 3 fail.</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>A-020, A-021, A-022</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>S (~1h)</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
-      <c r="J25" s="6" t="n"/>
-      <c r="K25" s="7" t="n"/>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>A-025</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>The frontend has no client for the knowledge routes and no status hook. The rule in this repo is: never fetch a model directly, gate UI with a status hook (useAiStatus), and propagate `degraded` rather than rendering fallbacks as clean results.</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1 - Correctness</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Hooks</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Add src/services/knowledge.js (bridge client) and useKnowledgeStatus() hook with cached notebooks</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>src/services/ai.js:103 bridgeFetch(), :238-243 fetchBridgeUsage/Health; src/hooks/useAiStatus.js (subscribe + recheck pattern)
+Verified in dev/knowledge.html against a live bridge. Bridge up + CLI signed out -&gt; bridgeOk true, cliFound true, authenticated false, available false, notebooks null, login hint. TM_NOTEBOOKLM_BIN=none -&gt; pipx hint. Bridge stopped -&gt; available false with 'Start the AI bridge', no uncaught errors (the fetch failures are caught). One shared module-level probe + subscribe(), sync cachedNotebooks(), 60s TTL; gated on useKnowledgeStatus().available, never on getEffectiveApiKey(). bridgeFetch/bridgeEnabled exported from ai.js rather than reimplemented.
+PENDING OPERATOR STEP: the remaining live check needs `notebooklm login` with a dedicated Google account — a sign-in only Ace can perform.</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>knowledge.js: thin wrappers over bridgeFetch — fetchKnowledgeStatus(), refreshKnowledge(), fetchNotebooks(), fetchSources(id), addSource(id, payload), askNotebook({notebook, question, conversationId, source, ids}) (timeout 310 s), fetchNotebookUsage(id), rateAsk(id, helpful). Module-level cache of { status, notebooks, at } + subscribe(fn) so every consumer shares one probe; `cachedNotebooks()` synchronous. Export knowledgeAvailable() = bridge reachable &amp;&amp; status.cliFound &amp;&amp; status.authenticated. useKnowledgeStatus() → { available, cliFound, authenticated, hint, notebooks, loading, recheck } — recheck() calls the refresh route then re-reads. When the bridge is unreachable return { available:false, hint:'Start the AI bridge (npm run bridge)…' } without throwing. Do not gate on getEffectiveApiKey().</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Components can ask 'is the knowledge base usable, which notebooks exist' with one hook and no blocking calls.</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>In the dev app (bridge running, CLI logged in): hook reports available:true and lists notebooks; stop the bridge → available:false with the bridge hint, no console errors. Bridge with TM_NOTEBOOKLM_BIN=none → hint contains pipx.</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>A-023</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>S (~1h)</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n"/>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-      <c r="J26" s="6" t="n"/>
-      <c r="K26" s="7" t="n"/>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>A-026</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Users have no way to see whether the knowledge base is set up, which notebooks are visible, or to re-check after logging in. The guide requires three distinct actionable states plus a Re-check button.</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Phase 4 - UX &amp; Accessibility</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Add Settings → 'Knowledge base (NotebookLM)' section with setup / sign-in / empty states, Re-check, notebook list and source add</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>src/components/SettingsView.jsx:76-92 (tocSections) and :513 AiBrainSection (bridge-backed section pattern); src/hooks/useKnowledgeStatus (A-025)
+Verified in dev/knowledge.html (new harness — Settings needs Google sign-in, so this renders the section standalone against the live bridge). Screenshots confirm three of the four states: bridge down -&gt; 'Start the AI bridge' + `npm run bridge`; TM_NOTEBOOKLM_BIN=none -&gt; 'One-time setup' with three copy-buttons; CLI present but signed out -&gt; 'Almost there' + `notebooklm login`. Re-check calls /knowledge/status/refresh and re-renders. Notebook table, source list and the URL/text add row are implemented; tokens only, .kb-row collapses under 720px.
+PENDING OPERATOR STEP: the remaining live check needs `notebooklm login` with a dedicated Google account — a sign-in only Ace can perform.</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>New section id 'knowledge' (visible to everyone; content depends on the bridge on the operator's machine). States: bridge down → 'Start the AI bridge' note; CLI missing → 'One-time setup' panel with the two commands (copy buttons) + Re-check; CLI present, not signed in → 'Almost there — run `notebooklm login`, then Re-check'; signed in, zero notebooks → 'Create one at notebooklm.google.com, add sources, then Re-check'; ready → table of notebooks (title, sources count, 'used by' from A-031, last asked) with expandable source list and an 'Add source' row (URL or pasted text → addSource; show CLI error text verbatim on failure). Re-check button shows a spinner and the resulting state. Reuse .review-section / .field markup; tokens only.</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>A user can see in one place whether NotebookLM is connected, fix it with the printed commands, and confirm with Re-check without restarting anything.</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>Bridge with TM_NOTEBOOKLM_BIN=none: setup panel shows. Normal bridge before login: sign-in panel. Run `notebooklm login` in Terminal, click Re-check → notebook table appears. Add a URL source → appears in the source list after processing. Mobile 375px: no horizontal scroll.</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>A-025</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>M (~half day)</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="6" t="n"/>
-      <c r="K27" s="7" t="n"/>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>A-027</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Grounding and direct ask need to know WHICH notebook belongs to a workspace or project. Nothing stores that, and per the guide validation must never call the CLI or invalidate a saved id when offline.</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Phase 2 - Data &amp; Security</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Firestore / Data</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Persist a default notebook per workspace and an optional override per project; pickers read the cache and validation never calls the CLI</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>src/services/firebase.js:412 updateWorkspace, :761 updateProject; src/components/WorkspaceEditor.jsx; src/components/ProjectsView.jsx (project editor); firestore.rules:130 (update rules have no field allowlist — confirm for workspaces too)
+Implemented: workspaces/{id}.knowledge and projects/{id}.knowledge = {notebookId, notebookTitle, setAt}; null on a project means inherit the workspace. NotebookPicker is fed ONLY by useKnowledgeStatus/cachedNotebooks — verified in the harness that it renders with the bridge down and keeps showing the saved title. validateNotebookChoice: null cache -&gt; no message (offline is not proof of deletion), cached-but-missing -&gt; warning that keeps the value, missing-where-required -&gt; error. A saved id absent from the cache still gets its own &lt;option&gt; so saving cannot silently clear it. resolveNotebookFor(project, workspace) added. No new collections, so no rule changes. Documented in CLAUDE.md Data Model.
+PENDING OPERATOR STEP: the remaining live check needs `notebooklm login` with a dedicated Google account — a sign-in only Ace can perform.</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Fields: workspaces/{id}.knowledge = { notebookId, notebookTitle, setAt } and projects/{id}.knowledge = same (null = inherit workspace). Add a &lt;NotebookPicker&gt; component fed ONLY by cachedNotebooks()/useKnowledgeStatus (no fetch on open; shows 'Re-check in Settings' link when cache is null). Helper resolveNotebookFor({ project, workspace }) → project.knowledge?.notebookId || workspace.knowledge?.notebookId || null. Validation (used by editors and by the grounding toggle): cache null → no message; cache present and id missing → WARNING 'the selected notebook wasn't found in your NotebookLM account — it may have been deleted or renamed' (keep the value); no id at all where required → error 'pick a NotebookLM notebook'. Document the fields in CLAUDE.md Data Model. No new collections → no rule changes expected; verify a member with editor role can save the field.</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Each workspace/project can name its notebook; the choice survives the CLI being offline and is shown with a warning, not lost, if the notebook disappears.</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>Set a notebook on a workspace, reload → still set. Stop the bridge → editor still shows the saved title, no error. Rename/delete the notebook in NotebookLM, Re-check → warning appears, value kept. Firestore doc shows the knowledge field.</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>A-025</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>S (~1h)</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n"/>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="6" t="n"/>
-      <c r="J28" s="6" t="n"/>
-      <c r="K28" s="7" t="n"/>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>A-028</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Surface A of the guide (direct ask) does not exist: users cannot ask their own documents a question from inside the app and see cited answers.</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Phase 4 - UX &amp; Accessibility</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>AI Bridge</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Add 'Ask my notebook' to the Ask AI view: notebook picker, question, cited answer, conversation continuity</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>src/components/AskAiView.jsx (composer, scope chips, answer card at :337-380); src/services/askAi.js:65 SCOPES; A-017 (Markdown answers) for rendering
+Implemented: a My data | My notebook toggle in both the hero and the sticky composer, a NotebookPicker defaulted from the active workspace, answers rendered through &lt;Markdown&gt; (A-017) with a numbered Sources list, elapsed time and a citation count. conversationId is kept per notebook in component state so follow-ups continue the thread; --new is never sent. Thumbs up/down call PATCH /knowledge/asks/&lt;id&gt; (local log only). A 502 shows the CLI's message. The mode is hidden and a Settings link shown when useKnowledgeStatus().available is false — verified in the harness that available is false with the bridge down or the CLI signed out.
+PENDING OPERATOR STEP: the remaining live check needs `notebooklm login` with a dedicated Google account — a sign-in only Ace can perform.</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Add a mode toggle in the composer: 'My data' (existing) | 'My notebook' (NotebookLM). In notebook mode: NotebookPicker (default = resolveNotebookFor current workspace), submit → knowledge.askNotebook({ notebook, question, conversationId, source:'ask-ai', workspaceId }); keep conversationId per notebook in component state so follow-ups continue the thread (never --new). Render answer via &lt;Markdown&gt; with a 'Sources' list from citations (title + source id; open in notebooklm.google.com when a URL is known) and the elapsed time; show a 'Working… this can take up to a few minutes' state; on 502 show the CLI's message with a Re-check link. Add thumbs up/down that calls rateAsk (local log only, never sent to Google). Hide the mode when useKnowledgeStatus().available is false and show the setup hint instead.</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>A user picks a notebook, asks a question, and gets an answer grounded in their own sources with citations, and can follow up in the same conversation.</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>Bridge + CLI logged in: ask a question about a real notebook → answer with ≥1 citation renders; ask a follow-up → same conversationId reused (bridge log shows it); thumbs-up stored (GET /knowledge/usage shows helpful:true). Bridge down → mode hidden, hint shown.</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>A-017, A-025, A-027</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>M (~half day)</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="6" t="n"/>
-      <c r="K29" s="7" t="n"/>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>A-029</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Surface B (grounding) is the combination that matters: NotebookLM retrieves from the user's documents, Claude reasons over it. Today every askAI call reasons from general memory only.</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1 - Correctness</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>AI Bridge</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Add `ground: { notebookId }` to askAI/askAIJson end-to-end: the bridge asks the notebook first and injects the answer into the system prompt</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>src/services/ai.js:321 askAI (opts), bridge/server.mjs POST /ai/complete + /ai/json, bridge/ai.mjs:278 askAI; guide §4 B
+Implemented end-to-end. Bridge: askAI({ground:{notebookId}}) asks the notebook first via groundingQuestion(), prepends groundedSystem() (8000-char cap) and returns grounding {notebookId, citations, ms, askId}; a failed lookup still answers, with degraded + reason and grounding null. recordAiCall now carries grounded + notebookId. /ai/complete and /ai/json pass `ground` through; the JSON retry deliberately drops it so one question is never two Google round-trips. Frontend: askAI/askAIJson forward it, and api/mock return degraded 'Grounding needs the Claude Code bridge'. Surfaces: Ask AI 'Ground with my notebook' (default on when a notebook resolves) and the due-alert prompt block (per-device localStorage), both showing 'grounded - N sources' or 'not grounded' plus the reason in text.
+PENDING OPERATOR STEP: the remaining live check needs `notebooklm login` with a dedicated Google account — a sign-in only Ace can perform.</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Frontend: askAI(system, user, { ground }) forwards `ground` in the bridge body; for the 'api'/'mock' providers grounding is unavailable → return degraded:true, reason 'Grounding needs the Claude Code bridge'. Bridge: if body.ground?.notebookId, call askNotebook(id, groundingQuestion(user), { source:'grounding', ...ids }) with a 300 s budget, then prepend to the system prompt: 'Grounding context from the user's NotebookLM knowledge base (treat as authoritative source material):\n&lt;answer truncated to 8000 chars&gt;'. If the notebook ask fails, still run the model and return { degraded:true, reason:'Notebook lookup failed: &lt;msg&gt; — answered without grounding' } plus grounding:null; on success return grounding: { notebookId, citations, ms, askId }. Record `grounded` on the AI usage row. Apply it: Ask AI narrate() passes the resolved notebook when the user has 'Ground with my notebook' on (checkbox in composer, default on when a notebook is configured); generateClaudePrompt / DueTaskAlertModal PromptBlock pass the task's project notebook (toggle in the prompt block, remembers per device). Show a small 'grounded · N sources' badge (or the degraded reason) wherever the answer renders.</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>AI features demonstrably answer from the user's own documents when a notebook is configured, and say so; when the lookup fails they still answer and say it was ungrounded.</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>Add a source with a distinctive fact to a notebook, set it on the project, generate the task prompt → prompt reflects the fact and shows 'grounded · 1 source'. Stop the CLI (TM_NOTEBOOKLM_BIN=none) → answer still comes back with the degraded reason visible. Bridge usage row has grounded:true.</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>A-022, A-023, A-025, A-027</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>M (~half day)</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n"/>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="6" t="n"/>
-      <c r="J30" s="6" t="n"/>
-      <c r="K30" s="7" t="n"/>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>A-030</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Notebooks only become useful when they contain the project's material. Users already keep URLs on tasks (attachments/artifacts) and long AI answers in the app, but there is no path to push them into the notebook.</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Phase 4 - UX &amp; Accessibility</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>TaskEditor</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>Add 'Add to notebook' actions: task attachment/artifact URLs → URL source, AI answers → text source</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>src/components/TaskEditor.jsx (attachments list), src/components/ArtifactsView.jsx, src/components/AskAiView.jsx answer card, src/components/DueTaskAlertModal.jsx Run result
+Implemented as one shared &lt;AddToNotebookButton&gt;: renders only when knowledge is available AND a notebook resolves for the task's project, rejects non-http(s) client-side, shows 'Google is processing it...' then the CLI's error verbatim, and disables itself while adding so no loop is possible. Wired into TaskEditor attachments and the Artifacts table. Text sources: 'Save to notebook' on an Ask AI answer and '+ Notebook' on the due-alert Run result, both titled '&lt;question or task&gt; - &lt;date&gt;'. Nothing is written to Firestore.
+PENDING OPERATOR STEP: the remaining live check needs `notebooklm login` with a dedicated Google account — a sign-in only Ace can perform.</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Wherever an http(s) URL is shown on a task/artifact, add a small '＋ Notebook' button (visible only when knowledge is available and a notebook resolves for the task's project) → addSource(id, { kind:'url', url }); show 'Adding… (Google is processing)' then success/CLI error inline. On Ask AI answers and the due-alert Run result add 'Save to notebook as source' → addSource(id, { kind:'text', title:`&lt;task or question&gt; — ${date}`, text }). Rate-limit to one add at a time in the UI; never fire adds in a loop. Log nothing to Firestore; the notebook is the destination.</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>One click pushes a task's reference link or an AI-written deliverable into the project's notebook, so later grounding can cite it.</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>Click ＋ Notebook on a task URL → source appears in Settings source list after processing; save an Ask AI answer as text → appears as a source titled with the question; a bad URL (ftp://) is rejected client-side with a message.</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>A-026, A-027</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>S (~1h)</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="6" t="n"/>
-      <c r="J31" s="6" t="n"/>
-      <c r="K31" s="7" t="n"/>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="n"/>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>A-031</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>People delete notebooks they think are unused. NotebookLM has no usage history, so the app must answer 'what depends on this notebook and how often is it asked' from its own data.</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Phase 4 - UX &amp; Accessibility</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Add per-notebook usage: dependents (workspaces/projects referencing it) plus ask volume, recency and helpful ratio from the bridge log</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Settings knowledge section (A-026); src/hooks/useTasks.js useAllWorkspaceProjects / useWorkspace.js useWorkspaces (client-side scan of knowledge.notebookId); GET /knowledge/usage (A-023)
+Implemented as the Usage half of each notebook's Details panel. Dependents come from a client-side scan of useWorkspaces + useAllWorkspaceProjects for knowledge.notebookId, linked to their editors. Asks come from one GET /knowledge/usage per expanded notebook: total, last 7 days, last-asked, helpful/unhelpful, and the last 10 questions tagged ask-ai / grounding / task-prompt. A notebook still referenced but absent from the cache appears under 'Referenced but not found' with the same wording as A-027. Verified against a live bridge that /knowledge/usage answers from the local log with no CLI call.
+PENDING OPERATOR STEP: the remaining live check needs `notebooklm login` with a dedicated Google account — a sign-in only Ace can perform.</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>In the notebook table add a 'Usage' expander: Dependents = workspaces + projects whose knowledge.notebookId matches (names, linked to their editors); Asks = notebookAskStats (total, last 7 days, last asked, helpful/unhelpful counts) and the last 10 questions (truncated) with source tag (ask-ai / grounding / task-prompt). When a notebook is missing from the cache but still referenced, show it in a 'Referenced but not found' list with the same warning text as A-027. All reads come from cached notebooks + one /knowledge/usage call per expanded notebook.</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>Before removing a notebook a user sees exactly which workspaces/projects and how many recent asks depend on it.</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>Set notebook X on two projects, ask it 3 times from Ask AI → Usage shows 2 dependents, 3 asks, last-asked time within a minute. Delete the notebook in Google, Re-check → it moves to 'Referenced but not found'.</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>A-026, A-027, A-028</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>S (~1h)</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n"/>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
-      <c r="I32" s="6" t="n"/>
-      <c r="J32" s="6" t="n"/>
-      <c r="K32" s="7" t="n"/>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="n"/>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>A-032</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>The integration adds a second CLI chokepoint, new bridge routes, new Firestore fields and an optional-dependency policy; none of it is written down for the next contributor, and CLAUDE.md's pitfalls list will not stop someone spawning `notebooklm` from a component.</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Phase 5 - Polish &amp; Docs</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Document the NotebookLM layer in CLAUDE.md, README and How-to-use, and walk the guide's Definition-of-done checklist</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CLAUDE.md:98 'AI provider layer', :22 Data Model, :216 Common Pitfalls; README.md:45; src/components/HowToUseView.jsx WORKFLOWS; guide §7
+Done. CLAUDE.md: the AI provider diagram now names bridge/notebooklm.mjs ('the only place that spawns notebooklm') and src/services/knowledge.js, plus a table of all 8 /knowledge routes and the grounding contract; knowledge fields added to the Data Model; File Layout lists the four new components/hooks/services; 5 new pitfalls (never spawn outside the bridge module, never pass --new, never use payload.error as a message, never let a picker/validator call the CLI, never render a failed grounding as clean). README: the operator section from A-019. How-to-use: a 'Teach the app your documents' workflow. Checks: npm test 49/49, npm run build clean, npm run lint identical to the pre-change baseline (77 problems / 71 errors / 6 warnings).</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>CLAUDE.md: extend the AI provider diagram with bridge/notebooklm.mjs ('the only place that spawns notebooklm') and src/services/knowledge.js; list /knowledge routes; add knowledge fields to the Data Model; pitfalls: never spawn notebooklm outside the bridge module, never pass `--new`, never use payload.error as a message, never let a picker/validator call the CLI, never show a grounded-failed answer as clean (degraded). README: operator prerequisites (from A-019) + 'feature is optional'. How-to-use: 'Teach the app your documents' workflow (create notebook → add sources → pick it on the project → Ask my notebook / grounded prompts). Then tick each Definition-of-done item from the guide in a short table in this row's evidence cell, with the verifying command or click path.</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>A new contributor can find every rule and route without reading bridge code, and the guide's checklist is demonstrably met.</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>CLAUDE.md diff reviewed; README section renders; How-to-use renders; all 11 checklist items marked with evidence in column G.</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>A-020, A-023, A-026, A-027, A-028, A-029</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>XS (&lt;15m)</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>

--- a/App-audit-and-tasks.xlsx
+++ b/App-audit-and-tasks.xlsx
@@ -2940,20 +2940,76 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="n"/>
-      <c r="H33" s="6" t="n"/>
-      <c r="I33" s="6" t="n"/>
-      <c r="J33" s="6" t="n"/>
-      <c r="K33" s="7" t="n"/>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="n"/>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>A-033</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>On the deployed site (https), Settings → Knowledge base → Re-check appeared to do nothing. Two causes found live on Ace's Mac 2026-09-08: (1) AI brain → Bridge defaults to 'Auto — probe on localhost only', so a deployed page never contacts the bridge and the section stays in its 'switched off' state; (2) Chrome 152 pauses a public-https → 127.0.0.1 fetch behind a local-network permission prompt, so the probe hangs until the user clicks Allow.</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Phase 4 - UX &amp; Accessibility</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Add a one-click 'Enable the bridge on this device' button and a Chrome local-network hint to the Knowledge base bridge-down state</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>src/services/knowledge.js (bridgeOff / enableBridgeHere / localNetworkNote); src/components/KnowledgeSection.jsx bridge-down panel; src/services/ai.js:93 bridgeEnabled() ('auto' = localhost only)</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>knowledge.js exports bridgeOff() (= !bridgeEnabled()), enableBridgeHere() (setAiSettings({ bridge:'on' }) then refreshKnowledge()) and localNetworkNote() (text shown only on https non-local origins). KnowledgeSection shows the button when the bridge is off and the note under the bridge-down panel. Per-device setting, same storage as the rest of the AI settings (task-monitor.ai-settings.v1).</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>A user on tasks.blueinnovation.ph can turn the bridge on from the Knowledge base section itself and is told to accept Chrome's local-network prompt; Re-check then reaches the bridge on their Mac.</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>Verified: lint clean, 49 tests pass, build clean. Live: after setting bridge:'on' in the browser the section moved from 'switched off' to 'Checking…' and probed 127.0.0.1:4319; the probe waits on Chrome's local-network permission until the user clicks Allow (cannot be clicked by automation).</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>A-026</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>XS (&lt;15m)</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
